--- a/artfynd/A 47761-2024 artfynd.xlsx
+++ b/artfynd/A 47761-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121146817</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146813</v>
+        <v>121146815</v>
       </c>
       <c r="B3" t="n">
-        <v>78334</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146815</v>
+        <v>121146813</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47761-2024 artfynd.xlsx
+++ b/artfynd/A 47761-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146815</v>
+        <v>121146813</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146813</v>
+        <v>121146815</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>79219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47761-2024 artfynd.xlsx
+++ b/artfynd/A 47761-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121146817</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146813</v>
+        <v>121146815</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146815</v>
+        <v>121146813</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47761-2024 artfynd.xlsx
+++ b/artfynd/A 47761-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146817</v>
+        <v>121146815</v>
       </c>
       <c r="B2" t="n">
-        <v>91985</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568581</v>
+        <v>568625</v>
       </c>
       <c r="R2" t="n">
-        <v>6556782</v>
+        <v>6556773</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146815</v>
+        <v>121146813</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146813</v>
+        <v>121146817</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,28 +917,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568625</v>
+        <v>568581</v>
       </c>
       <c r="R4" t="n">
-        <v>6556773</v>
+        <v>6556782</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47761-2024 artfynd.xlsx
+++ b/artfynd/A 47761-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121146815</v>
+        <v>121146817</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568625</v>
+        <v>568581</v>
       </c>
       <c r="R2" t="n">
-        <v>6556773</v>
+        <v>6556782</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146813</v>
+        <v>121146815</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -868,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146817</v>
+        <v>121146813</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +921,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568581</v>
+        <v>568625</v>
       </c>
       <c r="R4" t="n">
-        <v>6556782</v>
+        <v>6556773</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47761-2024 artfynd.xlsx
+++ b/artfynd/A 47761-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121146815</v>
+        <v>121146813</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121146813</v>
+        <v>121146815</v>
       </c>
       <c r="B4" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
